--- a/sheets/대금율보/검수/타이타닉.xlsx
+++ b/sheets/대금율보/검수/타이타닉.xlsx
@@ -4211,7 +4211,7 @@
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -4285,7 +4285,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I6" s="24"/>
@@ -4327,7 +4327,7 @@
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 林</t>
         </is>
       </c>
@@ -4355,7 +4355,7 @@
       <c r="I8" s="23"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 夾</t>
         </is>
       </c>
@@ -4402,7 +4402,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 夾</t>
         </is>
       </c>
@@ -4514,7 +4514,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -4571,7 +4571,7 @@
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰㳞</t>
         </is>
       </c>
@@ -4581,7 +4581,7 @@
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
@@ -4689,7 +4689,7 @@
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -4770,7 +4770,7 @@
       <c r="C20" s="23"/>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -4784,7 +4784,7 @@
       <c r="G20" s="23"/>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -4859,7 +4859,7 @@
       <c r="G22" s="24"/>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I22" s="24"/>

--- a/sheets/대금율보/검수/타이타닉.xlsx
+++ b/sheets/대금율보/검수/타이타닉.xlsx
@@ -4117,22 +4117,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="19.86" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="19.86" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="19.86" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="19.86" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="19.86" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="76.92" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="68.77" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="68.77" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="68.77" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="68.77" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="68.77" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="25" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="68.77" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="68.77" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="68.77" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="68.77" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="68.77" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="K12" s="28"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="68.77" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="68.77" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="68.77" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="68.77" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="68.77" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="68.77" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="K18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="68.77" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="K19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="68.77" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="K20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="68.77" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="K21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="68.77" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -4877,6 +4877,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
 </worksheet>
 </file>